--- a/DICCIONARIO_actualizable.xlsx
+++ b/DICCIONARIO_actualizable.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEYENDA" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DICCIONARIO'!$A$1:$F$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DICCIONARIO'!$A$1:$G$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,17 +82,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6AA7C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="002F4160"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007C6572"/>
+        <fgColor rgb="00C49A8B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6AA7C"/>
       </patternFill>
     </fill>
     <fill>
@@ -102,7 +102,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C49A8B"/>
+        <fgColor rgb="007C6572"/>
       </patternFill>
     </fill>
     <fill>
@@ -142,11 +142,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -183,19 +183,6 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="001D1D1B"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6AA7C"/>
-          <bgColor rgb="00C6AA7C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
         <color rgb="00FFFFFF"/>
       </font>
       <fill>
@@ -209,12 +196,25 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="001D1D1B"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="007C6572"/>
-          <bgColor rgb="007C6572"/>
+          <fgColor rgb="00C49A8B"/>
+          <bgColor rgb="00C49A8B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="001D1D1B"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6AA7C"/>
+          <bgColor rgb="00C6AA7C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -235,12 +235,12 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <color rgb="001D1D1B"/>
+        <color rgb="00FFFFFF"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C49A8B"/>
-          <bgColor rgb="00C49A8B"/>
+          <fgColor rgb="007C6572"/>
+          <bgColor rgb="007C6572"/>
         </patternFill>
       </fill>
     </dxf>
@@ -619,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,7 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -661,6 +662,11 @@
           <t>TEMA</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TEMA 2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -693,6 +699,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -713,6 +720,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -737,6 +745,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -757,6 +766,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -789,6 +799,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -813,6 +824,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -833,6 +845,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -853,6 +866,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -881,6 +895,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -913,6 +928,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -941,6 +957,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -973,6 +990,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -997,6 +1015,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1025,6 +1044,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1049,6 +1069,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1077,6 +1098,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1101,6 +1123,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1129,6 +1152,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1157,6 +1181,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1177,6 +1202,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1197,6 +1223,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1225,6 +1252,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1245,6 +1273,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1265,6 +1294,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1289,6 +1319,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1309,6 +1340,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1333,6 +1365,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1357,6 +1390,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1377,6 +1411,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G30" s="3" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1401,6 +1436,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G31" s="3" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1425,6 +1461,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1449,6 +1486,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1473,6 +1511,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G34" s="3" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1501,6 +1540,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1529,6 +1569,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1553,6 +1594,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1573,6 +1615,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1601,6 +1644,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1625,6 +1669,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G40" s="3" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1653,6 +1698,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1677,6 +1723,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1705,6 +1752,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1725,6 +1773,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G44" s="3" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1749,6 +1798,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1769,6 +1819,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G46" s="3" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1793,6 +1844,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1813,6 +1865,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1837,6 +1890,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1869,6 +1923,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G50" s="3" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1893,6 +1948,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1917,6 +1973,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1941,6 +1998,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G53" s="3" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1973,6 +2031,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G54" s="3" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1997,6 +2056,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2021,6 +2081,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2045,6 +2106,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2073,6 +2135,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2093,6 +2156,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2113,6 +2177,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2137,6 +2202,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2161,6 +2227,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2185,6 +2252,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2209,6 +2277,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2233,6 +2302,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2257,6 +2327,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2281,6 +2352,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2305,6 +2377,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2329,6 +2402,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2353,6 +2427,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2377,6 +2452,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2397,6 +2473,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2417,6 +2494,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2445,6 +2523,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2465,6 +2544,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2489,6 +2569,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2509,6 +2590,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G77" s="3" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2537,6 +2619,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G78" s="3" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2565,6 +2648,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G79" s="3" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2589,6 +2673,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G80" s="3" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2609,6 +2694,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G81" s="3" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2637,6 +2723,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2665,6 +2752,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G83" s="3" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2693,6 +2781,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G84" s="3" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2713,6 +2802,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2737,6 +2827,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2761,6 +2852,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2781,6 +2873,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G88" s="3" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2801,6 +2894,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G89" s="3" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2825,6 +2919,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2849,6 +2944,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2873,6 +2969,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2893,6 +2990,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G93" s="3" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2917,6 +3015,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G94" s="3" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2941,6 +3040,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2965,6 +3065,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G96" s="3" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2989,6 +3090,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3013,6 +3115,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3037,6 +3140,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3057,6 +3161,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G100" s="3" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3081,6 +3186,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3101,6 +3207,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3125,6 +3232,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G103" s="3" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3145,6 +3253,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3173,6 +3282,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3197,6 +3307,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3221,6 +3332,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3245,6 +3357,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G108" s="3" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3273,6 +3386,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3293,6 +3407,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G110" s="3" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3313,6 +3428,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G111" s="3" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3337,6 +3453,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3361,6 +3478,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G113" s="3" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -3385,6 +3503,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3409,6 +3528,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3433,6 +3553,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G116" s="3" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3453,6 +3574,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3473,6 +3595,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G118" s="3" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3493,6 +3616,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3517,6 +3641,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3541,6 +3666,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G121" s="3" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3565,6 +3691,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G122" s="3" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3589,6 +3716,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G123" s="3" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3613,6 +3741,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3637,6 +3766,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G125" s="3" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3657,6 +3787,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3677,6 +3808,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3701,6 +3833,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G128" s="3" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3725,6 +3858,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G129" s="3" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3749,6 +3883,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G130" s="3" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3773,6 +3908,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3793,6 +3929,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3817,6 +3954,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G133" s="3" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3841,6 +3979,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G134" s="3" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3861,6 +4000,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G135" s="3" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3885,6 +4025,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G136" s="3" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3909,6 +4050,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G137" s="3" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3929,6 +4071,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G138" s="3" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3953,6 +4096,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G139" s="3" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3977,6 +4121,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G140" s="3" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4001,6 +4146,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4029,6 +4175,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G142" s="3" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4053,6 +4200,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G143" s="3" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4077,6 +4225,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G144" s="3" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -4101,6 +4250,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G145" s="3" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -4125,6 +4275,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -4149,6 +4300,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G147" s="3" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -4177,6 +4329,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G148" s="3" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -4201,6 +4354,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G149" s="3" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -4225,6 +4379,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G150" s="3" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -4249,6 +4404,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G151" s="3" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -4273,6 +4429,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G152" s="3" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -4297,6 +4454,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G153" s="3" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4321,6 +4479,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G154" s="3" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -4345,6 +4504,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G155" s="3" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -4365,6 +4525,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G156" s="3" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -4389,6 +4550,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -4413,6 +4575,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G158" s="3" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -4441,6 +4604,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G159" s="3" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -4465,6 +4629,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -4489,6 +4654,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G161" s="3" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4509,6 +4675,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G162" s="3" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4529,6 +4696,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G163" s="3" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4553,6 +4721,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G164" s="3" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4577,6 +4746,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G165" s="3" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4597,6 +4767,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G166" s="3" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4621,6 +4792,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G167" s="3" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4645,6 +4817,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G168" s="3" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4669,6 +4842,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G169" s="3" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4693,6 +4867,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G170" s="3" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -4717,6 +4892,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G171" s="3" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4741,6 +4917,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G172" s="3" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4765,6 +4942,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G173" s="3" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4789,6 +4967,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G174" s="3" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4813,6 +4992,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G175" s="3" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4837,6 +5017,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G176" s="3" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4861,6 +5042,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G177" s="3" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4881,6 +5063,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G178" s="3" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4905,6 +5088,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G179" s="3" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4925,6 +5109,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G180" s="3" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -4949,6 +5134,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G181" s="3" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -4973,6 +5159,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G182" s="3" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -4993,6 +5180,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G183" s="3" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -5017,6 +5205,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G184" s="3" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -5041,6 +5230,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G185" s="3" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5065,6 +5255,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G186" s="3" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5089,6 +5280,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G187" s="3" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5113,6 +5305,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G188" s="3" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -5137,6 +5330,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G189" s="3" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5157,6 +5351,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G190" s="3" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -5181,6 +5376,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G191" s="3" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5205,6 +5401,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G192" s="3" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -5225,6 +5422,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G193" s="3" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5253,6 +5451,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G194" s="3" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -5273,6 +5472,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G195" s="3" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -5293,6 +5493,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G196" s="3" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -5317,6 +5518,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G197" s="3" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -5341,6 +5543,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G198" s="3" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -5365,6 +5568,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G199" s="3" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -5389,6 +5593,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G200" s="3" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -5413,6 +5618,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G201" s="3" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -5437,6 +5643,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G202" s="3" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -5461,6 +5668,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G203" s="3" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -5485,6 +5693,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G204" s="3" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -5509,6 +5718,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G205" s="3" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -5533,6 +5743,7 @@
           <t>Elementos de tienda/distribución</t>
         </is>
       </c>
+      <c r="G206" s="3" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -5557,6 +5768,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G207" s="3" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -5581,6 +5793,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -5605,6 +5818,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G209" s="3" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -5629,6 +5843,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G210" s="3" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -5653,6 +5868,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G211" s="3" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -5677,6 +5893,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G212" s="3" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -5701,6 +5918,7 @@
           <t>Oficios/roles</t>
         </is>
       </c>
+      <c r="G213" s="3" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -5725,6 +5943,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G214" s="3" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -5749,6 +5968,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G215" s="3" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -5773,6 +5993,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -5797,6 +6018,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G217" s="3" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -5821,6 +6043,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -5845,6 +6068,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G219" s="3" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -5869,6 +6093,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -5893,6 +6118,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -5925,6 +6151,7 @@
           <t>Materiales</t>
         </is>
       </c>
+      <c r="G222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -5949,6 +6176,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G223" s="3" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -5973,6 +6201,7 @@
           <t>Dibujo/Planos</t>
         </is>
       </c>
+      <c r="G224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -5997,6 +6226,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -6021,6 +6251,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -6041,6 +6272,7 @@
           <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
+      <c r="G227" s="3" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -6065,6 +6297,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -6089,6 +6322,7 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -6121,6 +6355,7 @@
           <t>Organización obra/maquinaria</t>
         </is>
       </c>
+      <c r="G230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -6153,6 +6388,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -6185,6 +6421,7 @@
           <t>Vocabulario construcción</t>
         </is>
       </c>
+      <c r="G232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -6209,37 +6446,914 @@
           <t>Sin clasificar</t>
         </is>
       </c>
+      <c r="G233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Cemento (n.m.)</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>Ciment (n.m.)</t>
+        </is>
+      </c>
+      <c r="C234" s="3" t="inlineStr">
+        <is>
+          <t>Cement (n.)</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr"/>
+      <c r="E234" s="3" t="inlineStr"/>
+      <c r="F234" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G234" s="3" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Bloque (n.m.)</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>Parpaing (n.m.)</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>Block (n.)</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr"/>
+      <c r="E235" s="3" t="inlineStr"/>
+      <c r="F235" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G235" s="3" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Granito (n.m.)</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>Granit (n.m.)</t>
+        </is>
+      </c>
+      <c r="C236" s="3" t="inlineStr">
+        <is>
+          <t>Granite (n.)</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr"/>
+      <c r="E236" s="3" t="inlineStr"/>
+      <c r="F236" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G236" s="3" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Madera contrachapada (n.f.+adj.)</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr">
+        <is>
+          <t>Bois contreplaqué (n.m.+adj.)</t>
+        </is>
+      </c>
+      <c r="C237" s="3" t="inlineStr">
+        <is>
+          <t>Plywood (n.)</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr"/>
+      <c r="E237" s="3" t="inlineStr"/>
+      <c r="F237" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G237" s="3" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Poliestireno (n.m.)</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>Polystyrène (n.m.)</t>
+        </is>
+      </c>
+      <c r="C238" s="3" t="inlineStr">
+        <is>
+          <t>Polystyrene (n.)</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr"/>
+      <c r="E238" s="3" t="inlineStr"/>
+      <c r="F238" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G238" s="3" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Aguas pluviales (n.f.pl.)</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr">
+        <is>
+          <t>Eaux pluviales (n.f.pl.)</t>
+        </is>
+      </c>
+      <c r="C239" s="3" t="inlineStr">
+        <is>
+          <t>Rainwater (n.)</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr"/>
+      <c r="E239" s="3" t="inlineStr"/>
+      <c r="F239" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G239" s="3" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Apoyo (n.m.)</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>Appui (n.m.)</t>
+        </is>
+      </c>
+      <c r="C240" s="3" t="inlineStr">
+        <is>
+          <t>Support (n.)</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr"/>
+      <c r="E240" s="3" t="inlineStr"/>
+      <c r="F240" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G240" s="3" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Arcilla (n.f.)</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr">
+        <is>
+          <t>Argile (n.f.)</t>
+        </is>
+      </c>
+      <c r="C241" s="3" t="inlineStr">
+        <is>
+          <t>Clay (n.)</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr"/>
+      <c r="E241" s="3" t="inlineStr"/>
+      <c r="F241" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G241" s="3" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Armadura (n.f.)</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr">
+        <is>
+          <t>Armature (n.f.)</t>
+        </is>
+      </c>
+      <c r="C242" s="3" t="inlineStr">
+        <is>
+          <t>Rebar/reinforcement (n.)</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr"/>
+      <c r="E242" s="3" t="inlineStr"/>
+      <c r="F242" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G242" s="3" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Baldosa (n.f.)</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr">
+        <is>
+          <t>Carreau (n.m.)</t>
+        </is>
+      </c>
+      <c r="C243" s="3" t="inlineStr">
+        <is>
+          <t>Tile (n.)</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Piastrella (n.f.)</t>
+        </is>
+      </c>
+      <c r="E243" s="3" t="inlineStr">
+        <is>
+          <t>Keramikfliese (n.f.)</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G243" s="3" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Bóveda (n.f.)</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr">
+        <is>
+          <t>Voûte (n.f.)</t>
+        </is>
+      </c>
+      <c r="C244" s="3" t="inlineStr">
+        <is>
+          <t>Vault (n.)</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Volta (n.f.)</t>
+        </is>
+      </c>
+      <c r="E244" s="3" t="inlineStr">
+        <is>
+          <t>Gewölbe (n.n.)</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G244" s="3" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Cablear (v.)</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Câbler (v.)</t>
+        </is>
+      </c>
+      <c r="C245" s="3" t="inlineStr">
+        <is>
+          <t>Wire (v.)</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr"/>
+      <c r="E245" s="3" t="inlineStr"/>
+      <c r="F245" s="3" t="inlineStr">
+        <is>
+          <t>Organización obra/maquinaria</t>
+        </is>
+      </c>
+      <c r="G245" s="3" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Cercha (n.f.)</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr">
+        <is>
+          <t>Treillis (n.m.)</t>
+        </is>
+      </c>
+      <c r="C246" s="3" t="inlineStr">
+        <is>
+          <t>Truss (n.)</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr"/>
+      <c r="E246" s="3" t="inlineStr"/>
+      <c r="F246" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G246" s="3" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Colector (n.m.)</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>Réseau séparatif (n.m.)</t>
+        </is>
+      </c>
+      <c r="C247" s="3" t="inlineStr">
+        <is>
+          <t>Sanitary sewer (n.)</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr"/>
+      <c r="E247" s="3" t="inlineStr"/>
+      <c r="F247" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G247" s="3" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Compresión (n.f.)</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr">
+        <is>
+          <t>Compression (n.f.)</t>
+        </is>
+      </c>
+      <c r="C248" s="3" t="inlineStr">
+        <is>
+          <t>Compression (n.)</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr"/>
+      <c r="E248" s="3" t="inlineStr"/>
+      <c r="F248" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Cumbrera (n.f.)</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>Faîtage (n.m.)</t>
+        </is>
+      </c>
+      <c r="C249" s="3" t="inlineStr">
+        <is>
+          <t>Ridge (n.)</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr"/>
+      <c r="E249" s="3" t="inlineStr"/>
+      <c r="F249" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Demolición (n.f.)</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr">
+        <is>
+          <t>Démolition (n.f.)</t>
+        </is>
+      </c>
+      <c r="C250" s="3" t="inlineStr">
+        <is>
+          <t>Demolition (n.)</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr"/>
+      <c r="E250" s="3" t="inlineStr"/>
+      <c r="F250" s="3" t="inlineStr">
+        <is>
+          <t>Organización obra/maquinaria</t>
+        </is>
+      </c>
+      <c r="G250" s="3" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Doble piel (n.f.+adj.)</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Double peau (n.f.+adj.)</t>
+        </is>
+      </c>
+      <c r="C251" s="3" t="inlineStr">
+        <is>
+          <t>Double skin (n.)</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr"/>
+      <c r="E251" s="3" t="inlineStr"/>
+      <c r="F251" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G251" s="3" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Drenaje (n.m.)</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr">
+        <is>
+          <t>Drainage (n.m.)</t>
+        </is>
+      </c>
+      <c r="C252" s="3" t="inlineStr">
+        <is>
+          <t>Drainage (n.)</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr"/>
+      <c r="E252" s="3" t="inlineStr"/>
+      <c r="F252" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G252" s="3" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Escuadra (n.f.)</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr">
+        <is>
+          <t>Équerre (n.f.)</t>
+        </is>
+      </c>
+      <c r="C253" s="3" t="inlineStr"/>
+      <c r="D253" s="3" t="inlineStr"/>
+      <c r="E253" s="3" t="inlineStr"/>
+      <c r="F253" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Estanco (adj.)</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr">
+        <is>
+          <t>Étanche (adj.)</t>
+        </is>
+      </c>
+      <c r="C254" s="3" t="inlineStr">
+        <is>
+          <t>Watertight (adj.)</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr"/>
+      <c r="E254" s="3" t="inlineStr"/>
+      <c r="F254" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G254" s="3" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Estanqueidad (n.f.)</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr">
+        <is>
+          <t>Étanchéité (n.f.)</t>
+        </is>
+      </c>
+      <c r="C255" s="3" t="inlineStr">
+        <is>
+          <t>Watertightness (n.)</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr"/>
+      <c r="E255" s="3" t="inlineStr"/>
+      <c r="F255" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G255" s="3" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Fábrica (n.f.)</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Usine (n.f.)</t>
+        </is>
+      </c>
+      <c r="C256" s="3" t="inlineStr"/>
+      <c r="D256" s="3" t="inlineStr"/>
+      <c r="E256" s="3" t="inlineStr"/>
+      <c r="F256" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G256" s="3" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Fibrocemento (n.m.)</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr">
+        <is>
+          <t>Fibre ciment (n.m.)</t>
+        </is>
+      </c>
+      <c r="C257" s="3" t="inlineStr">
+        <is>
+          <t>Fibre cement (n.)</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr"/>
+      <c r="E257" s="3" t="inlineStr"/>
+      <c r="F257" s="3" t="inlineStr">
+        <is>
+          <t>Elementos de tienda/distribución</t>
+        </is>
+      </c>
+      <c r="G257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Grieta (n.f.)</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>Fissure (n.f.)</t>
+        </is>
+      </c>
+      <c r="C258" s="3" t="inlineStr">
+        <is>
+          <t>Crack (n.)</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr"/>
+      <c r="E258" s="3" t="inlineStr"/>
+      <c r="F258" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Luz libre (n.f.+adj.)</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr">
+        <is>
+          <t>Portée (n.f.)</t>
+        </is>
+      </c>
+      <c r="C259" s="3" t="inlineStr">
+        <is>
+          <t>Clear span (n.)</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr"/>
+      <c r="E259" s="3" t="inlineStr"/>
+      <c r="F259" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Muro de carga (n.m.)</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Mur porteur (n.m.)</t>
+        </is>
+      </c>
+      <c r="C260" s="3" t="inlineStr">
+        <is>
+          <t>Load-bearing wall (n.)</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr"/>
+      <c r="E260" s="3" t="inlineStr"/>
+      <c r="F260" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G260" s="3" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Nervio (n.m.)</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr">
+        <is>
+          <t>Nervure (n.f.)</t>
+        </is>
+      </c>
+      <c r="C261" s="3" t="inlineStr">
+        <is>
+          <t>Rib (n.)</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr"/>
+      <c r="E261" s="3" t="inlineStr"/>
+      <c r="F261" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Panel (n.m.)</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>Panneau (n.m.)</t>
+        </is>
+      </c>
+      <c r="C262" s="3" t="inlineStr">
+        <is>
+          <t>Panel (n.)</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr"/>
+      <c r="E262" s="3" t="inlineStr"/>
+      <c r="F262" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Pavimento (n.m.)</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr">
+        <is>
+          <t>Pavement (n.m.)</t>
+        </is>
+      </c>
+      <c r="C263" s="3" t="inlineStr">
+        <is>
+          <t>Flooring (n.)</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr"/>
+      <c r="E263" s="3" t="inlineStr"/>
+      <c r="F263" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Puntal (n.m.)</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr">
+        <is>
+          <t>Étai (n.m.)</t>
+        </is>
+      </c>
+      <c r="C264" s="3" t="inlineStr">
+        <is>
+          <t>Prop (n.)</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr"/>
+      <c r="E264" s="3" t="inlineStr"/>
+      <c r="F264" s="3" t="inlineStr">
+        <is>
+          <t>Organización obra/maquinaria</t>
+        </is>
+      </c>
+      <c r="G264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Recepción (n.f.)</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr">
+        <is>
+          <t>Réception (n.f.)</t>
+        </is>
+      </c>
+      <c r="C265" s="3" t="inlineStr"/>
+      <c r="D265" s="3" t="inlineStr"/>
+      <c r="E265" s="3" t="inlineStr"/>
+      <c r="F265" s="3" t="inlineStr">
+        <is>
+          <t>Organización obra/maquinaria</t>
+        </is>
+      </c>
+      <c r="G265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Sedimento (n.m.)</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr">
+        <is>
+          <t>Sédiment (n.m.)</t>
+        </is>
+      </c>
+      <c r="C266" s="3" t="inlineStr">
+        <is>
+          <t>Sediment (n.)</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="3" t="inlineStr"/>
+      <c r="F266" s="3" t="inlineStr">
+        <is>
+          <t>Materiales</t>
+        </is>
+      </c>
+      <c r="G266" s="3" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Sanear (v.)</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Assainir (v.)</t>
+        </is>
+      </c>
+      <c r="C267" s="3" t="inlineStr"/>
+      <c r="D267" s="3" t="inlineStr"/>
+      <c r="E267" s="3" t="inlineStr"/>
+      <c r="F267" s="3" t="inlineStr">
+        <is>
+          <t>Vocabulario construcción</t>
+        </is>
+      </c>
+      <c r="G267" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F233"/>
+  <autoFilter ref="A1:G267"/>
   <conditionalFormatting sqref="F2:F1000">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Vocabulario construcción"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="1">
       <formula>"Materiales"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="2">
+      <formula>"Organización obra/maquinaria"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="3">
+      <formula>"Oficios/roles"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="4">
       <formula>"Elementos de tienda/distribución"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+    <cfRule type="cellIs" priority="11" operator="equal" dxfId="5">
+      <formula>"Dibujo/Planos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="13" operator="equal" dxfId="6">
+      <formula>"Presupuesto/gestión/administración"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="15" operator="equal" dxfId="7">
+      <formula>"Sin clasificar"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G1000">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
+      <formula>"Vocabulario construcción"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="1">
+      <formula>"Materiales"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Organización obra/maquinaria"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="3">
+      <formula>"Oficios/roles"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="equal" dxfId="4">
+      <formula>"Elementos de tienda/distribución"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="equal" dxfId="5">
+      <formula>"Dibujo/Planos"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="equal" dxfId="6">
       <formula>"Presupuesto/gestión/administración"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" dxfId="5">
-      <formula>"Dibujo/Planos"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" dxfId="6">
-      <formula>"Oficios/roles"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" dxfId="7">
+    <cfRule type="cellIs" priority="16" operator="equal" dxfId="7">
       <formula>"Sin clasificar"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoría no válida" error="Elige una categoría de la lista (hoja LEYENDA)." type="list">
+    <dataValidation sqref="F2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoría no válida" error="Elige una categoría de la lista (hoja LEYENDA)." type="list">
       <formula1>=LEYENDA!$A$2:$A$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -6262,7 +7376,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Categorías válidas para la columna TEMA (se eligen en el desplegable)</t>
+          <t>Categorías válidas para TEMA y TEMA 2 (se eligen en el desplegable)</t>
         </is>
       </c>
     </row>
@@ -6283,21 +7397,21 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>Elementos de tienda/distribución</t>
+          <t>Organización obra/maquinaria</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Organización obra/maquinaria</t>
+          <t>Oficios/roles</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Presupuesto/gestión/administración</t>
+          <t>Elementos de tienda/distribución</t>
         </is>
       </c>
     </row>
@@ -6311,7 +7425,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>Oficios/roles</t>
+          <t>Presupuesto/gestión/administración</t>
         </is>
       </c>
     </row>
